--- a/southern_europe/Results_CCSchainOptimization/technology_selection/Summary.xlsx
+++ b/southern_europe/Results_CCSchainOptimization/technology_selection/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE24"/>
+  <dimension ref="A1:AE29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2955,6 +2955,521 @@
       <c r="AE24" t="inlineStr">
         <is>
           <t>Results_CCSchainOptimization\technology_selection\20261018093956_tax250_emissions_minC_technology_selection-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2400385774.088739</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4807697.932922915</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8283173.663982717</v>
+      </c>
+      <c r="E25" t="n">
+        <v>602505.6276120057</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8283173.663982717</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5410203.560534921</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1476860.173172902</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2385215536.691049</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2400385774.088739</v>
+      </c>
+      <c r="N25" t="n">
+        <v>15901436.91127363</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>15901436.91127363</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>15901436.91127363</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>496.0099999904633</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2364399007.880182</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2400385774.088739</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>35986766.20855761</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>tax150_costs_technology_selection</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Results_CCSchainOptimization\technology_selection\20261019133421_tax150_costs_technology_selection-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2855294783.713433</v>
+      </c>
+      <c r="B26" t="n">
+        <v>301960241.5017623</v>
+      </c>
+      <c r="C26" t="n">
+        <v>181940113.0272092</v>
+      </c>
+      <c r="D26" t="n">
+        <v>992729203.6765851</v>
+      </c>
+      <c r="E26" t="n">
+        <v>31504648.04244501</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1294689445.178347</v>
+      </c>
+      <c r="G26" t="n">
+        <v>213444761.0696542</v>
+      </c>
+      <c r="H26" t="n">
+        <v>842024743.1808735</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>505135834.2845578</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2855294783.713433</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2020543.33713819</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2020543.33713819</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2020543.337138188</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>147146.9370000362</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2812488174.611456</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2855294783.713433</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>42806609.10197687</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>tax250_costs_technology_selection</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Results_CCSchainOptimization\technology_selection\20261019135754_tax250_costs_technology_selection-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2748516906.948057</v>
+      </c>
+      <c r="B27" t="n">
+        <v>296614740.4634299</v>
+      </c>
+      <c r="C27" t="n">
+        <v>176069250.788945</v>
+      </c>
+      <c r="D27" t="n">
+        <v>985992608.970294</v>
+      </c>
+      <c r="E27" t="n">
+        <v>28344975.68795447</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1282607349.433724</v>
+      </c>
+      <c r="G27" t="n">
+        <v>204414226.4768994</v>
+      </c>
+      <c r="H27" t="n">
+        <v>790866406.5441463</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>470628924.4932876</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2748516906.948057</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2353144.622466408</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2353144.622466408</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2353144.62246641</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>96881.99099993706</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2707964603.536625</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2748516906.948057</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>40552303.41143227</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>tax200_costs_technology_selection</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Results_CCSchainOptimization\technology_selection\20261021070654_tax200_costs_technology_selection-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6897208915.836252</v>
+      </c>
+      <c r="B28" t="n">
+        <v>283641139.393212</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3852927621.200023</v>
+      </c>
+      <c r="D28" t="n">
+        <v>922046343.7631255</v>
+      </c>
+      <c r="E28" t="n">
+        <v>330154084.6052364</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1205687483.156337</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4183081705.805259</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1095267645.360413</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>413172081.5142419</v>
+      </c>
+      <c r="M28" t="n">
+        <v>6897208915.836252</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1652688.326056918</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1652688.326056918</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1652688.326056917</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>24.79499983787537</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1652688.326056959</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1652688.326056918</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-4.144385457038879e-08</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>emissions_minC</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>tax250_emissions_minC_technology_selection</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Results_CCSchainOptimization\technology_selection\20261022102006_tax250_emissions_minC_technology_selection-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2914465451.42947</v>
+      </c>
+      <c r="B29" t="n">
+        <v>282969853.3600925</v>
+      </c>
+      <c r="C29" t="n">
+        <v>199313923.1853414</v>
+      </c>
+      <c r="D29" t="n">
+        <v>921781252.0152167</v>
+      </c>
+      <c r="E29" t="n">
+        <v>38659839.44564761</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1204751105.375309</v>
+      </c>
+      <c r="G29" t="n">
+        <v>237973762.630989</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1058155329.827422</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>413585253.5957496</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2914465451.42947</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1654341.014382975</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1654341.014382975</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1654341.014382951</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>10892.86500000954</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2871985944.817352</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2914465451.42947</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>42479506.61211777</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>emissions_minC</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>tax250_emissions_minC_technology_selection</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Results_CCSchainOptimization\technology_selection\20261022102101_tax250_emissions_minC_technology_selection-1</t>
         </is>
       </c>
     </row>
